--- a/hall/resources/sample/InteractionAreasTable.xlsx
+++ b/hall/resources/sample/InteractionAreasTable.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -100,7 +100,7 @@
     <t>建筑等级上限</t>
   </si>
   <si>
-    <t>设备数量上限</t>
+    <t>设备ID</t>
   </si>
   <si>
     <t>接待上限(人)</t>
@@ -115,6 +115,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>List&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -142,82 +145,124 @@
     <t>机台区域1</t>
   </si>
   <si>
+    <t>10101_10102_10103</t>
+  </si>
+  <si>
     <t>1_2</t>
   </si>
   <si>
     <t>机台区域2</t>
   </si>
   <si>
+    <t>10201_10202_10203</t>
+  </si>
+  <si>
     <t>1_3</t>
   </si>
   <si>
     <t>捕鱼桌区域</t>
   </si>
   <si>
+    <t>10301_10302_10303</t>
+  </si>
+  <si>
     <t>1_4</t>
   </si>
   <si>
     <t>扑克桌区域</t>
   </si>
   <si>
+    <t>10401_10402_10403</t>
+  </si>
+  <si>
     <t>1_11</t>
   </si>
   <si>
     <t>普通休息区</t>
   </si>
   <si>
+    <t>11101_11102_11103</t>
+  </si>
+  <si>
     <t>2_1</t>
   </si>
   <si>
     <t>VIP机台区域1</t>
   </si>
   <si>
+    <t>20101_20102_20103</t>
+  </si>
+  <si>
     <t>2_2</t>
   </si>
   <si>
     <t>VIP机台区域2</t>
   </si>
   <si>
+    <t>20201_20202_20203</t>
+  </si>
+  <si>
     <t>2_3</t>
   </si>
   <si>
     <t>VIP机台区域3</t>
   </si>
   <si>
+    <t>20301_20302_20303</t>
+  </si>
+  <si>
     <t>2_4</t>
   </si>
   <si>
     <t>VIP机台区域4</t>
   </si>
   <si>
+    <t>20401_20402_20403</t>
+  </si>
+  <si>
     <t>2_10</t>
   </si>
   <si>
     <t>VIP休息区</t>
   </si>
   <si>
+    <t>21001_21002_21003</t>
+  </si>
+  <si>
     <t>2_5</t>
   </si>
   <si>
     <t>VIP捕鱼桌区域1</t>
   </si>
   <si>
+    <t>20501_20502_20502</t>
+  </si>
+  <si>
     <t>2_6</t>
   </si>
   <si>
     <t>VIP捕鱼桌区域2</t>
   </si>
   <si>
+    <t>20601_20602_20603</t>
+  </si>
+  <si>
     <t>2_7</t>
   </si>
   <si>
     <t>VIP扑克桌区域1</t>
   </si>
   <si>
+    <t>20701_20702_20703</t>
+  </si>
+  <si>
     <t>2_8</t>
   </si>
   <si>
     <t>VIP扑克桌区域2</t>
+  </si>
+  <si>
+    <t>20801_20802_20803</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1302,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>9</v>
@@ -1271,27 +1316,27 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:9">
@@ -1313,16 +1358,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="3">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G5" s="3">
         <v>8</v>
@@ -1342,16 +1387,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3">
-        <v>8</v>
-      </c>
-      <c r="F6" s="3">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="G6" s="3">
         <v>8</v>
@@ -1371,16 +1416,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>8</v>
-      </c>
-      <c r="F7" s="3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="G7" s="3">
         <v>4</v>
@@ -1400,16 +1445,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E8" s="3">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="G8" s="3">
         <v>4</v>
@@ -1429,16 +1474,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E9" s="3">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="G9" s="3">
         <v>10</v>
@@ -1458,16 +1503,16 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E10" s="3">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="G10" s="3">
         <v>8</v>
@@ -1487,16 +1532,16 @@
         <v>2</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="G11" s="3">
         <v>8</v>
@@ -1516,16 +1561,16 @@
         <v>2</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="G12" s="3">
         <v>8</v>
@@ -1545,16 +1590,16 @@
         <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E13" s="3">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="G13" s="3">
         <v>8</v>
@@ -1574,16 +1619,16 @@
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E14" s="3">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="G14" s="3">
         <v>20</v>
@@ -1603,16 +1648,16 @@
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E15" s="3">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="G15" s="3">
         <v>4</v>
@@ -1632,16 +1677,16 @@
         <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E16" s="3">
-        <v>8</v>
-      </c>
-      <c r="F16" s="3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="G16" s="3">
         <v>4</v>
@@ -1661,16 +1706,16 @@
         <v>2</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E17" s="3">
-        <v>8</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="G17" s="3">
         <v>4</v>
@@ -1690,16 +1735,16 @@
         <v>2</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3">
-        <v>8</v>
-      </c>
-      <c r="F18" s="3">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="G18" s="3">
         <v>4</v>
